--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\.claude\worktrees\residual-headers-conditionals-021ab5\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\.claude\worktrees\bridge-cse_01CECbFAThBCAdeR5ZRcns7Y\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F65382-2CF4-4770-9945-DD862A38544B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4277C5C-F7C6-406E-A4F7-783169E2384B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="1050" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression Instructions" sheetId="2" r:id="rId1"/>
@@ -60,322 +60,323 @@
     <t>Define your model in the MODEL SPECIFICATION block (columns A–L):</t>
   </si>
   <si>
+    <t>For each included Predictor, set its Type. Continuous predictors enter the design matrix as-is. Categorical predictors are dummy-coded automatically: each level except the reference level becomes a 0/1 column with a level-qualified name (e.g. "Status: Developing"). The reference level defaults to the first level in sort order; type a level into Reference Level to override it (the cell turns red if that level does not exist in the analysis sample). The Levels and Reference In Use columns display what the model will do: the distinct level count in the analysis sample, and the reference actually in effect. A categorical with one level (or an invalid reference) is flagged red and contributes no columns — the rest of the model still computes.</t>
+  </si>
+  <si>
+    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order and Transform columns are placeholders for a future version and are not read by any formula; they are hidden on the sheet. The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1.</t>
+  </si>
+  <si>
+    <t>Intercept:</t>
+  </si>
+  <si>
+    <t>The Intercept toggle sits at the top of the Include column (C2). Leave it TRUE for models with Categorical predictors: reference-level dummy coding relies on the intercept to carry the baseline, and the toggle flags red if it is FALSE while a Categorical predictor is included.</t>
+  </si>
+  <si>
+    <t>Which rows are used:</t>
+  </si>
+  <si>
+    <t>The analysis sample is derived automatically — a row is included when the Response is numeric, every included Continuous predictor is numeric, and every Filter column is truthy. There is nothing to configure beyond the Roles. Note that Categorical predictors impose no completeness requirement: rows with a blank category still enter the sample (all of that variable's dummies are blank there) unless a Filter excludes them.</t>
+  </si>
+  <si>
+    <t>Optional — point prediction:</t>
+  </si>
+  <si>
+    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AH) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (Y12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
+  </si>
+  <si>
+    <t>REGRESSION DIAGNOSTIC GUIDE</t>
+  </si>
+  <si>
+    <t>Use the charts and flagged cells on the Regression sheet to assess model assumptions. Work through Tier 1 first; investigate Tier 2 only when a Tier 1 plot raises a concern.</t>
+  </si>
+  <si>
+    <t>TIER 1 — Review for every model</t>
+  </si>
+  <si>
+    <t>Plot</t>
+  </si>
+  <si>
+    <t>X-axis</t>
+  </si>
+  <si>
+    <t>Y-axis</t>
+  </si>
+  <si>
+    <t>What to look for</t>
+  </si>
+  <si>
+    <t>Residuals vs. Fitted</t>
+  </si>
+  <si>
+    <t>Predicted Y</t>
+  </si>
+  <si>
+    <t>Residuals</t>
+  </si>
+  <si>
+    <t>Random scatter around zero. A curve or funnel shape signals nonlinearity or heteroscedasticity (non-constant error variance).</t>
+  </si>
+  <si>
+    <t>Normal Q-Q</t>
+  </si>
+  <si>
+    <t>Normal Scores (theoretical)</t>
+  </si>
+  <si>
+    <t>Studentized Residuals Ranked</t>
+  </si>
+  <si>
+    <t>Points close to a straight diagonal line. Heavy tails or an S-curve indicate non-normal errors. Check QQ Correlation (Cell P10): below 0.98 = mild concern, below 0.95 = stronger concern.</t>
+  </si>
+  <si>
+    <t>Actual vs. Predicted</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Points close to a 45° line. A bow or fan shape confirms the same problems seen in Residuals vs. Fitted but from a different angle.</t>
+  </si>
+  <si>
+    <t>TIER 2 — Investigate when Tier 1 raises a concern</t>
+  </si>
+  <si>
+    <t>Scale-Location</t>
+  </si>
+  <si>
+    <t>Scale-Location
+(√|Studentized Residuals|)</t>
+  </si>
+  <si>
+    <t>Flat horizontal spread of points = homoscedasticity. An upward trend confirms heteroscedasticity flagged in Tier 1. Yellow cells: value &gt; √2 ≈ 1.41; red cells: value &gt; √3 ≈ 1.73.</t>
+  </si>
+  <si>
+    <t>Cook's Distance</t>
+  </si>
+  <si>
+    <t>Observation (bar position)</t>
+  </si>
+  <si>
+    <t>Spikes above 4/n (yellow) or above 0.9 (red) mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a different population, or disproportionately distorts the analysis. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
+  </si>
+  <si>
+    <t>Studentized Residuals vs. Leverage</t>
+  </si>
+  <si>
+    <t>Hat Diagonal (leverage)</t>
+  </si>
+  <si>
+    <t>Studentized Residuals</t>
+  </si>
+  <si>
+    <t>High leverage alone is not a problem. Combined high leverage and large residual (top-right or bottom-right of the plot) = influential outlier. Hat &gt; 2p/n is flagged red; Hat &gt; 3p/n is additionally bold.</t>
+  </si>
+  <si>
+    <t>PRESS Residuals</t>
+  </si>
+  <si>
+    <t>PRESS Residual
+(e / (1 − h))</t>
+  </si>
+  <si>
+    <t>PRESS residuals inflate the ordinary residual by leverage. Bars are ordered by observation number. Large values (|PRESS| &gt; 2 × SE yellow, &gt; 3 × SE red) flag observations whose removal would substantially shift the fitted model.</t>
+  </si>
+  <si>
+    <t>DIAGNOSTIC THRESHOLD REFERENCE</t>
+  </si>
+  <si>
+    <t>Diagnostic</t>
+  </si>
+  <si>
+    <t>Location on sheet</t>
+  </si>
+  <si>
+    <t>Yellow threshold</t>
+  </si>
+  <si>
+    <t>Red threshold</t>
+  </si>
+  <si>
+    <t>GVIF (Generalized Variance Inflation Factor)</t>
+  </si>
+  <si>
+    <t>Col U, Predictor Summary</t>
+  </si>
+  <si>
+    <t>GVIF &gt; 5  (possible collinearity)</t>
+  </si>
+  <si>
+    <t>GVIF &gt; 10  (strong collinearity)</t>
+  </si>
+  <si>
+    <t>Tolerance</t>
+  </si>
+  <si>
+    <t>Col V, Predictor Summary</t>
+  </si>
+  <si>
+    <t>Tolerance &lt; 0.2</t>
+  </si>
+  <si>
+    <t>Tolerance &lt; 0.1</t>
+  </si>
+  <si>
+    <t>PRESS R²</t>
+  </si>
+  <si>
+    <t>Cell P5, Diagnostics</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>PRESS R² &lt; 0  (worse than predicting Y-mean)</t>
+  </si>
+  <si>
+    <t>QQ Correlation</t>
+  </si>
+  <si>
+    <t>Cell P10, Diagnostics</t>
+  </si>
+  <si>
+    <t>&lt; 0.98  (mild non-normality)</t>
+  </si>
+  <si>
+    <t>&lt; 0.95  (clear non-normality)</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Cell Q15, ANOVA Table</t>
+  </si>
+  <si>
+    <t>P-value &gt; alpha  (model not significant)</t>
+  </si>
+  <si>
+    <t>Coefficient P-values</t>
+  </si>
+  <si>
+    <t>Col P, Coefficients</t>
+  </si>
+  <si>
+    <t>P-value &gt; alpha  (term not significant)</t>
+  </si>
+  <si>
+    <t>Col AB, Residual Output</t>
+  </si>
+  <si>
+    <t>h &gt; 2p/n  (high leverage)</t>
+  </si>
+  <si>
+    <t>Col AC, Residual Output</t>
+  </si>
+  <si>
+    <t>|r*| &gt; 2  (moderate outlier)</t>
+  </si>
+  <si>
+    <t>|r*| ≥ 3  (strong outlier)</t>
+  </si>
+  <si>
+    <t>Col AD, Residual Output</t>
+  </si>
+  <si>
+    <t>D &gt; 4/n  (review)</t>
+  </si>
+  <si>
+    <t>D &gt; 0.9  (high influence)</t>
+  </si>
+  <si>
+    <t>Col AG, Residual Output</t>
+  </si>
+  <si>
+    <t>&gt; √2 ≈ 1.41  (|r*| &gt; 2 equivalent)</t>
+  </si>
+  <si>
+    <t>&gt; √3 ≈ 1.73  (|r*| &gt; 3 equivalent)</t>
+  </si>
+  <si>
+    <t>PRESS Residual</t>
+  </si>
+  <si>
+    <t>Col AH, Residual Output</t>
+  </si>
+  <si>
+    <t>|PRESS| &gt; 2 × SE</t>
+  </si>
+  <si>
+    <t>|PRESS| &gt; 3 × SE</t>
+  </si>
+  <si>
+    <t>COMMON PATTERNS AND NEXT STEPS</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Symptom</t>
+  </si>
+  <si>
+    <t>Next step</t>
+  </si>
+  <si>
+    <t>Heteroscedasticity
+(funnel residuals)</t>
+  </si>
+  <si>
+    <t>Residuals vs. Fitted shows fan shape; Scale-Location trends upward.</t>
+  </si>
+  <si>
+    <t>Consider: log-transforming Y, adding polynomial terms, or fitting a Weighted Least Squares (WLS) model. WLS is planned for a future version of this library.</t>
+  </si>
+  <si>
+    <t>Nonlinearity
+(curved residuals)</t>
+  </si>
+  <si>
+    <t>Residuals vs. Fitted shows a curve; Actual vs. Predicted bows.</t>
+  </si>
+  <si>
+    <t>Add squared or interaction terms to the model. Toggle individual predictors on/off to isolate which variable is driving the curve.</t>
+  </si>
+  <si>
+    <t>Non-normal errors
+(Q-Q deviation)</t>
+  </si>
+  <si>
+    <t>Q-Q plot shows heavy tails or S-curve; QQ Correlation &lt; 0.98.</t>
+  </si>
+  <si>
+    <t>With n &gt; 100 moderate departures rarely invalidate inference. For small n, consider robust standard errors or a bootstrap Confidence Interval approach.</t>
+  </si>
+  <si>
+    <t>Influential observations
+(high Cook's D or PRESS)</t>
+  </si>
+  <si>
+    <t>Cook's D &gt; 4/n or |PRESS| &gt; 2 × SE for one or more rows.</t>
+  </si>
+  <si>
+    <t>Inspect those rows. Verify data entry. Refit without the observation(s) and compare coefficients — if they shift substantially, see which ones and research the reasons why those data points are different. If there's a significant difference, choose one model, but report the prediction results of the other regression as a sensitivity analysis.</t>
+  </si>
+  <si>
+    <t>Multicollinearity
+(high GVIF)</t>
+  </si>
+  <si>
+    <t>GVIF &gt; 10 for one or more predictors. A categorical predictor's dummy columns all show the same shared GVIF value — that's the whole variable's collinearity, not a per-level artifact.</t>
+  </si>
+  <si>
+    <t>Remove or combine correlated predictors. Use the Correlation_Matrix function to identify the pairs. Partial R² shows each predictor's unique contribution after controlling for the others.</t>
+  </si>
+  <si>
     <t>The Variable column fills itself from your table's headers — one specification row per column. For each row, choose a Role:
 Response (y) — the dependent variable; declare exactly one.
 Predictor (x) — a candidate model input; the Include toggle turns it on or off for the current model run.
 Identifier (Row Label) — labeling columns such as names, IDs, or dates; they appear as row labels in the RESIDUAL OUTPUT section (multiple Identifier columns are joined with "|").
 Filter — a TRUE/FALSE or 1/0 column; only rows where every Filter column is truthy enter the regression. Declare several Filter columns to stratify — they are ANDed together.
-Omit — never used for anything; helper columns and notes.</t>
-  </si>
-  <si>
-    <t>For each included Predictor, set its Type. Continuous predictors enter the design matrix as-is. Categorical predictors are dummy-coded automatically: each level except the reference level becomes a 0/1 column with a level-qualified name (e.g. "Status: Developing"). The reference level defaults to the first level in sort order; type a level into Reference Level to override it (the cell turns red if that level does not exist in the analysis sample). The Levels and Reference In Use columns display what the model will do: the distinct level count in the analysis sample, and the reference actually in effect. A categorical with one level (or an invalid reference) is flagged red and contributes no columns — the rest of the model still computes.</t>
-  </si>
-  <si>
-    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order and Transform columns are placeholders for a future version and are not read by any formula; they are hidden on the sheet. The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1.</t>
-  </si>
-  <si>
-    <t>Intercept:</t>
-  </si>
-  <si>
-    <t>The Intercept toggle sits at the top of the Include column (C2). Leave it TRUE for models with Categorical predictors: reference-level dummy coding relies on the intercept to carry the baseline, and the toggle flags red if it is FALSE while a Categorical predictor is included.</t>
-  </si>
-  <si>
-    <t>Which rows are used:</t>
-  </si>
-  <si>
-    <t>The analysis sample is derived automatically — a row is included when the Response is numeric, every included Continuous predictor is numeric, and every Filter column is truthy. There is nothing to configure beyond the Roles. Note that Categorical predictors impose no completeness requirement: rows with a blank category still enter the sample (all of that variable's dummies are blank there) unless a Filter excludes them.</t>
-  </si>
-  <si>
-    <t>Optional — point prediction:</t>
-  </si>
-  <si>
-    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AH) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (Y12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
-  </si>
-  <si>
-    <t>REGRESSION DIAGNOSTIC GUIDE</t>
-  </si>
-  <si>
-    <t>Use the charts and flagged cells on the Regression sheet to assess model assumptions. Work through Tier 1 first; investigate Tier 2 only when a Tier 1 plot raises a concern.</t>
-  </si>
-  <si>
-    <t>TIER 1 — Review for every model</t>
-  </si>
-  <si>
-    <t>Plot</t>
-  </si>
-  <si>
-    <t>X-axis</t>
-  </si>
-  <si>
-    <t>Y-axis</t>
-  </si>
-  <si>
-    <t>What to look for</t>
-  </si>
-  <si>
-    <t>Residuals vs. Fitted</t>
-  </si>
-  <si>
-    <t>Predicted Y</t>
-  </si>
-  <si>
-    <t>Residuals</t>
-  </si>
-  <si>
-    <t>Random scatter around zero. A curve or funnel shape signals nonlinearity or heteroscedasticity (non-constant error variance).</t>
-  </si>
-  <si>
-    <t>Normal Q-Q</t>
-  </si>
-  <si>
-    <t>Normal Scores (theoretical)</t>
-  </si>
-  <si>
-    <t>Studentized Residuals Ranked</t>
-  </si>
-  <si>
-    <t>Points close to a straight diagonal line. Heavy tails or an S-curve indicate non-normal errors. Check QQ Correlation (Cell P10): below 0.98 = mild concern, below 0.95 = stronger concern.</t>
-  </si>
-  <si>
-    <t>Actual vs. Predicted</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Points close to a 45° line. A bow or fan shape confirms the same problems seen in Residuals vs. Fitted but from a different angle.</t>
-  </si>
-  <si>
-    <t>TIER 2 — Investigate when Tier 1 raises a concern</t>
-  </si>
-  <si>
-    <t>Scale-Location</t>
-  </si>
-  <si>
-    <t>Scale-Location
-(√|Studentized Residuals|)</t>
-  </si>
-  <si>
-    <t>Flat horizontal spread of points = homoscedasticity. An upward trend confirms heteroscedasticity flagged in Tier 1. Yellow cells: value &gt; √2 ≈ 1.41; red cells: value &gt; √3 ≈ 1.73.</t>
-  </si>
-  <si>
-    <t>Cook's Distance</t>
-  </si>
-  <si>
-    <t>Observation (bar position)</t>
-  </si>
-  <si>
-    <t>Spikes above 4/n (yellow) or above 0.9 (red) mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a different population, or disproportionately distorts the analysis. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
-  </si>
-  <si>
-    <t>Studentized Residuals vs. Leverage</t>
-  </si>
-  <si>
-    <t>Hat Diagonal (leverage)</t>
-  </si>
-  <si>
-    <t>Studentized Residuals</t>
-  </si>
-  <si>
-    <t>High leverage alone is not a problem. Combined high leverage and large residual (top-right or bottom-right of the plot) = influential outlier. Hat &gt; 2p/n is flagged red; Hat &gt; 3p/n is additionally bold.</t>
-  </si>
-  <si>
-    <t>PRESS Residuals</t>
-  </si>
-  <si>
-    <t>PRESS Residual
-(e / (1 − h))</t>
-  </si>
-  <si>
-    <t>PRESS residuals inflate the ordinary residual by leverage. Bars are ordered by observation number. Large values (|PRESS| &gt; 2 × SE yellow, &gt; 3 × SE red) flag observations whose removal would substantially shift the fitted model.</t>
-  </si>
-  <si>
-    <t>DIAGNOSTIC THRESHOLD REFERENCE</t>
-  </si>
-  <si>
-    <t>Diagnostic</t>
-  </si>
-  <si>
-    <t>Location on sheet</t>
-  </si>
-  <si>
-    <t>Yellow threshold</t>
-  </si>
-  <si>
-    <t>Red threshold</t>
-  </si>
-  <si>
-    <t>GVIF (Generalized Variance Inflation Factor)</t>
-  </si>
-  <si>
-    <t>Col U, Predictor Summary</t>
-  </si>
-  <si>
-    <t>GVIF &gt; 5  (possible collinearity)</t>
-  </si>
-  <si>
-    <t>GVIF &gt; 10  (strong collinearity)</t>
-  </si>
-  <si>
-    <t>Tolerance</t>
-  </si>
-  <si>
-    <t>Col V, Predictor Summary</t>
-  </si>
-  <si>
-    <t>Tolerance &lt; 0.2</t>
-  </si>
-  <si>
-    <t>Tolerance &lt; 0.1</t>
-  </si>
-  <si>
-    <t>PRESS R²</t>
-  </si>
-  <si>
-    <t>Cell P5, Diagnostics</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>PRESS R² &lt; 0  (worse than predicting Y-mean)</t>
-  </si>
-  <si>
-    <t>QQ Correlation</t>
-  </si>
-  <si>
-    <t>Cell P10, Diagnostics</t>
-  </si>
-  <si>
-    <t>&lt; 0.98  (mild non-normality)</t>
-  </si>
-  <si>
-    <t>&lt; 0.95  (clear non-normality)</t>
-  </si>
-  <si>
-    <t>Significance F</t>
-  </si>
-  <si>
-    <t>Cell Q15, ANOVA Table</t>
-  </si>
-  <si>
-    <t>P-value &gt; alpha  (model not significant)</t>
-  </si>
-  <si>
-    <t>Coefficient P-values</t>
-  </si>
-  <si>
-    <t>Col P, Coefficients</t>
-  </si>
-  <si>
-    <t>P-value &gt; alpha  (term not significant)</t>
-  </si>
-  <si>
-    <t>Col AB, Residual Output</t>
-  </si>
-  <si>
-    <t>h &gt; 2p/n  (high leverage)</t>
-  </si>
-  <si>
-    <t>Col AC, Residual Output</t>
-  </si>
-  <si>
-    <t>|r*| &gt; 2  (moderate outlier)</t>
-  </si>
-  <si>
-    <t>|r*| ≥ 3  (strong outlier)</t>
-  </si>
-  <si>
-    <t>Col AD, Residual Output</t>
-  </si>
-  <si>
-    <t>D &gt; 4/n  (review)</t>
-  </si>
-  <si>
-    <t>D &gt; 0.9  (high influence)</t>
-  </si>
-  <si>
-    <t>Col AG, Residual Output</t>
-  </si>
-  <si>
-    <t>&gt; √2 ≈ 1.41  (|r*| &gt; 2 equivalent)</t>
-  </si>
-  <si>
-    <t>&gt; √3 ≈ 1.73  (|r*| &gt; 3 equivalent)</t>
-  </si>
-  <si>
-    <t>PRESS Residual</t>
-  </si>
-  <si>
-    <t>Col AH, Residual Output</t>
-  </si>
-  <si>
-    <t>|PRESS| &gt; 2 × SE</t>
-  </si>
-  <si>
-    <t>|PRESS| &gt; 3 × SE</t>
-  </si>
-  <si>
-    <t>COMMON PATTERNS AND NEXT STEPS</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Symptom</t>
-  </si>
-  <si>
-    <t>Next step</t>
-  </si>
-  <si>
-    <t>Heteroscedasticity
-(funnel residuals)</t>
-  </si>
-  <si>
-    <t>Residuals vs. Fitted shows fan shape; Scale-Location trends upward.</t>
-  </si>
-  <si>
-    <t>Consider: log-transforming Y, adding polynomial terms, or fitting a Weighted Least Squares (WLS) model. WLS is planned for a future version of this library.</t>
-  </si>
-  <si>
-    <t>Nonlinearity
-(curved residuals)</t>
-  </si>
-  <si>
-    <t>Residuals vs. Fitted shows a curve; Actual vs. Predicted bows.</t>
-  </si>
-  <si>
-    <t>Add squared or interaction terms to the model. Toggle individual predictors on/off to isolate which variable is driving the curve.</t>
-  </si>
-  <si>
-    <t>Non-normal errors
-(Q-Q deviation)</t>
-  </si>
-  <si>
-    <t>Q-Q plot shows heavy tails or S-curve; QQ Correlation &lt; 0.98.</t>
-  </si>
-  <si>
-    <t>With n &gt; 100 moderate departures rarely invalidate inference. For small n, consider robust standard errors or a bootstrap Confidence Interval approach.</t>
-  </si>
-  <si>
-    <t>Influential observations
-(high Cook's D or PRESS)</t>
-  </si>
-  <si>
-    <t>Cook's D &gt; 4/n or |PRESS| &gt; 2 × SE for one or more rows.</t>
-  </si>
-  <si>
-    <t>Inspect those rows. Verify data entry. Refit without the observation(s) and compare coefficients — if they shift substantially, see which ones and research the reasons why those data points are different. If there's a significant difference, choose one model, but report the prediction results of the other regression as a sensitivity analysis.</t>
-  </si>
-  <si>
-    <t>Multicollinearity
-(high GVIF)</t>
-  </si>
-  <si>
-    <t>GVIF &gt; 10 for one or more predictors. A categorical predictor's dummy columns all show the same shared GVIF value — that's the whole variable's collinearity, not a per-level artifact.</t>
-  </si>
-  <si>
-    <t>Remove or combine correlated predictors. Use the Correlation_Matrix function to identify the pairs. Partial R² shows each predictor's unique contribution after controlling for the others.</t>
+Omit — never used for anything; helper columns and notes.
+Fixed Effects — declare exactly one panel-grouping variable; the model absorbs a separate intercept per group (one-way within transformation) instead of pooled OLS, crediting the absorbed degrees of freedom back into inference. Type and Reference Level don't apply to this row — leave them as-is.</t>
   </si>
 </sst>
 </file>
@@ -810,49 +811,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="135" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="150" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +873,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -880,12 +881,12 @@
     </row>
     <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -893,63 +894,63 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -957,77 +958,77 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1035,243 +1036,243 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="240" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\.claude\worktrees\bridge-cse_01CECbFAThBCAdeR5ZRcns7Y\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\.claude\worktrees\3-0-changeover-stage-3-263d53\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4277C5C-F7C6-406E-A4F7-783169E2384B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C3CE199-38F8-42C4-B598-08D44514720F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression Instructions" sheetId="2" r:id="rId1"/>
@@ -57,15 +57,9 @@
     <t>Open the Name Manager (Formulas → Name Manager) and update Source_Table (the "Refers To" field) to your table, including its header row — for example =MyTable[#All]. Everything else derives from this one name: the header row, the data body, and the variable list in the MODEL SPECIFICATION block all update automatically. Source_Table points at MileageData by default; a second sample table, LifeExpectancyData (on the Life Expectancy Data sheet), ships with the workbook if you want to practice this retarget before pointing at your own data.</t>
   </si>
   <si>
-    <t>Define your model in the MODEL SPECIFICATION block (columns A–L):</t>
-  </si>
-  <si>
     <t>For each included Predictor, set its Type. Continuous predictors enter the design matrix as-is. Categorical predictors are dummy-coded automatically: each level except the reference level becomes a 0/1 column with a level-qualified name (e.g. "Status: Developing"). The reference level defaults to the first level in sort order; type a level into Reference Level to override it (the cell turns red if that level does not exist in the analysis sample). The Levels and Reference In Use columns display what the model will do: the distinct level count in the analysis sample, and the reference actually in effect. A categorical with one level (or an invalid reference) is flagged red and contributes no columns — the rest of the model still computes.</t>
   </si>
   <si>
-    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order and Transform columns are placeholders for a future version and are not read by any formula; they are hidden on the sheet. The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1.</t>
-  </si>
-  <si>
     <t>Intercept:</t>
   </si>
   <si>
@@ -79,9 +73,6 @@
   </si>
   <si>
     <t>Optional — point prediction:</t>
-  </si>
-  <si>
-    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AH) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (Y12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
   </si>
   <si>
     <t>REGRESSION DIAGNOSTIC GUIDE</t>
@@ -377,6 +368,15 @@
 Filter — a TRUE/FALSE or 1/0 column; only rows where every Filter column is truthy enter the regression. Declare several Filter columns to stratify — they are ANDed together.
 Omit — never used for anything; helper columns and notes.
 Fixed Effects — declare exactly one panel-grouping variable; the model absorbs a separate intercept per group (one-way within transformation) instead of pooled OLS, crediting the absorbed degrees of freedom back into inference. Type and Reference Level don't apply to this row — leave them as-is.</t>
+  </si>
+  <si>
+    <t>Define your model in the MODEL SPECIFICATION block (columns A–O):</t>
+  </si>
+  <si>
+    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — results are not converted back to raw units. Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
+  </si>
+  <si>
+    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
   </si>
 </sst>
 </file>
@@ -808,52 +808,52 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="150" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="300" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +873,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -881,12 +881,12 @@
     </row>
     <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -894,63 +894,63 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -958,77 +958,77 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1036,243 +1036,243 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="240" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\.claude\worktrees\3-0-changeover-stage-3-263d53\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C3CE199-38F8-42C4-B598-08D44514720F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59ADFA01-E38B-4F00-B7B0-532E4364F778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
@@ -373,10 +373,10 @@
     <t>Define your model in the MODEL SPECIFICATION block (columns A–O):</t>
   </si>
   <si>
-    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — results are not converted back to raw units. Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
-  </si>
-  <si>
     <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
+  </si>
+  <si>
+    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG3:AH9 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH4 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
   </si>
 </sst>
 </file>
@@ -821,9 +821,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="300" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="360" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -853,7 +853,7 @@
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59ADFA01-E38B-4F00-B7B0-532E4364F778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEA7A817-D997-4774-BCA8-EAF20A08EF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\local_python\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEA7A817-D997-4774-BCA8-EAF20A08EF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FEBC25A-861C-407D-A72E-8BD6708F4DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression Instructions" sheetId="2" r:id="rId1"/>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\local_python\Statistical_Analysis_Lambda_Catalog\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FEBC25A-861C-407D-A72E-8BD6708F4DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{726E6D12-2812-47B4-85E5-97A3FBEDEBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression Instructions" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
   <si>
     <t>How to use the Regression sheet for Multilinear Regression (MLR)</t>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG3:AH9 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH4 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
+  </si>
+  <si>
+    <t>Optional – faster charts on a fixed-size dataset:</t>
+  </si>
+  <si>
+    <t>The seven diagnostic charts read each series from a worksheet-scoped named range (the RegChart* names) built with OFFSET and sized to the live observation count at $Y$8. OFFSET is volatile, so those ranges re-evaluate on every recalculation pass. If your dataset size is stable, you can remove that overhead by pointing each chart series directly at the absolute range the name resolves to — from row 3 (one below the column header) down to row 2+N, where N is the count shown at $Y$8 (for 200 observations, for example ='Regression'!$AM$3:$AM$202). Select the chart, click a series, and replace the ='Regression'!RegChart... reference in the formula bar with the absolute range. The trade-off is that the chart no longer resizes if you add or drop rows — you must re-point it when the row count changes. The named ranges can stay defined; there is no need to delete them.</t>
   </si>
 </sst>
 </file>
@@ -775,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7F67BA-2205-467F-84E2-8C770A21BFE9}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -854,6 +860,16 @@
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{726E6D12-2812-47B4-85E5-97A3FBEDEBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF1288E7-5987-4580-AA2A-95E8B54AEAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>Point the sheet at your data (one edit):</t>
   </si>
   <si>
-    <t>Open the Name Manager (Formulas → Name Manager) and update Source_Table (the "Refers To" field) to your table, including its header row — for example =MyTable[#All]. Everything else derives from this one name: the header row, the data body, and the variable list in the MODEL SPECIFICATION block all update automatically. Source_Table points at MileageData by default; a second sample table, LifeExpectancyData (on the Life Expectancy Data sheet), ships with the workbook if you want to practice this retarget before pointing at your own data.</t>
-  </si>
-  <si>
     <t>For each included Predictor, set its Type. Continuous predictors enter the design matrix as-is. Categorical predictors are dummy-coded automatically: each level except the reference level becomes a 0/1 column with a level-qualified name (e.g. "Status: Developing"). The reference level defaults to the first level in sort order; type a level into Reference Level to override it (the cell turns red if that level does not exist in the analysis sample). The Levels and Reference In Use columns display what the model will do: the distinct level count in the analysis sample, and the reference actually in effect. A categorical with one level (or an invalid reference) is flagged red and contributes no columns — the rest of the model still computes.</t>
   </si>
   <si>
@@ -383,6 +380,9 @@
   </si>
   <si>
     <t>The seven diagnostic charts read each series from a worksheet-scoped named range (the RegChart* names) built with OFFSET and sized to the live observation count at $Y$8. OFFSET is volatile, so those ranges re-evaluate on every recalculation pass. If your dataset size is stable, you can remove that overhead by pointing each chart series directly at the absolute range the name resolves to — from row 3 (one below the column header) down to row 2+N, where N is the count shown at $Y$8 (for 200 observations, for example ='Regression'!$AM$3:$AM$202). Select the chart, click a series, and replace the ='Regression'!RegChart... reference in the formula bar with the absolute range. The trade-off is that the chart no longer resizes if you add or drop rows — you must re-point it when the row count changes. The named ranges can stay defined; there is no need to delete them.</t>
+  </si>
+  <si>
+    <t>Open the Name Manager (Formulas → Name Manager) and update Source_Table (the "Refers To" field) to your table, including its header row — for example =MyTable[#All]. Everything else derives from this one name: the header row, the data body, and the variable list in the MODEL SPECIFICATION block all update automatically. Source_Table points at LifeExpectancyData by default (a curated four-driver Life Expectancy model — Adult Mortality, Alcohol, percentage expenditure, and Status); a second sample table, MileageData (on the Mileage Data sheet), ships with the workbook for a multi-level categorical-encoding demo (MPG ~ Horsepower + Weight + C(Model Year) + C(Origin) — reach it with --regression-dataset auto_mpg). Practice the retarget on either before pointing at your own data.</t>
   </si>
 </sst>
 </file>
@@ -807,69 +807,69 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="360" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -889,7 +889,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -897,12 +897,12 @@
     </row>
     <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -910,63 +910,63 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -974,77 +974,77 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1052,243 +1052,243 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="240" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF1288E7-5987-4580-AA2A-95E8B54AEAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A0C5438-B4BF-49C3-BE62-93CA8175CDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="109">
   <si>
     <t>How to use the Regression sheet for Multilinear Regression (MLR)</t>
   </si>
@@ -245,39 +245,18 @@
     <t>Coefficient P-values</t>
   </si>
   <si>
-    <t>Col P, Coefficients</t>
-  </si>
-  <si>
     <t>P-value &gt; alpha  (term not significant)</t>
   </si>
   <si>
-    <t>Col AB, Residual Output</t>
-  </si>
-  <si>
     <t>h &gt; 2p/n  (high leverage)</t>
   </si>
   <si>
-    <t>Col AC, Residual Output</t>
-  </si>
-  <si>
     <t>|r*| &gt; 2  (moderate outlier)</t>
   </si>
   <si>
     <t>|r*| ≥ 3  (strong outlier)</t>
   </si>
   <si>
-    <t>Col AD, Residual Output</t>
-  </si>
-  <si>
-    <t>D &gt; 4/n  (review)</t>
-  </si>
-  <si>
-    <t>D &gt; 0.9  (high influence)</t>
-  </si>
-  <si>
-    <t>Col AG, Residual Output</t>
-  </si>
-  <si>
     <t>&gt; √2 ≈ 1.41  (|r*| &gt; 2 equivalent)</t>
   </si>
   <si>
@@ -285,9 +264,6 @@
   </si>
   <si>
     <t>PRESS Residual</t>
-  </si>
-  <si>
-    <t>Col AH, Residual Output</t>
   </si>
   <si>
     <t>|PRESS| &gt; 2 × SE</t>
@@ -383,6 +359,27 @@
   </si>
   <si>
     <t>Open the Name Manager (Formulas → Name Manager) and update Source_Table (the "Refers To" field) to your table, including its header row — for example =MyTable[#All]. Everything else derives from this one name: the header row, the data body, and the variable list in the MODEL SPECIFICATION block all update automatically. Source_Table points at LifeExpectancyData by default (a curated four-driver Life Expectancy model — Adult Mortality, Alcohol, percentage expenditure, and Status); a second sample table, MileageData (on the Mileage Data sheet), ships with the workbook for a multi-level categorical-encoding demo (MPG ~ Horsepower + Weight + C(Model Year) + C(Origin) — reach it with --regression-dataset auto_mpg). Practice the retarget on either before pointing at your own data.</t>
+  </si>
+  <si>
+    <t>Col AE, Coefficients</t>
+  </si>
+  <si>
+    <t>Col AR, Residual Output</t>
+  </si>
+  <si>
+    <t>Col AS, Residual Output</t>
+  </si>
+  <si>
+    <t>Col AT, Residual Output</t>
+  </si>
+  <si>
+    <t>D &gt; F.INV(0.5, p, n-p)  (high influence)</t>
+  </si>
+  <si>
+    <t>Col AW, Residual Output</t>
+  </si>
+  <si>
+    <t>Col AX, Residual Output</t>
   </si>
 </sst>
 </file>
@@ -809,17 +806,17 @@
     </row>
     <row r="6" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="90" x14ac:dyDescent="0.25">
@@ -829,7 +826,7 @@
     </row>
     <row r="11" spans="1:1" ht="360" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -859,17 +856,17 @@
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1139,13 +1136,13 @@
         <v>66</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1153,13 +1150,13 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1167,13 +1164,13 @@
         <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1181,13 +1178,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1195,100 +1192,100 @@
         <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="240" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows code\Statistical_Analysis_Lambda_Catalog\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows_code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A0C5438-B4BF-49C3-BE62-93CA8175CDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33FE3A67-F0AF-4703-B8DD-ACF62AC8A03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
@@ -145,9 +145,6 @@
     <t>Observation (bar position)</t>
   </si>
   <si>
-    <t>Spikes above 4/n (yellow) or above 0.9 (red) mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a different population, or disproportionately distorts the analysis. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
-  </si>
-  <si>
     <t>Studentized Residuals vs. Leverage</t>
   </si>
   <si>
@@ -316,9 +313,6 @@
   <si>
     <t>Influential observations
 (high Cook's D or PRESS)</t>
-  </si>
-  <si>
-    <t>Cook's D &gt; 4/n or |PRESS| &gt; 2 × SE for one or more rows.</t>
   </si>
   <si>
     <t>Inspect those rows. Verify data entry. Refit without the observation(s) and compare coefficients — if they shift substantially, see which ones and research the reasons why those data points are different. If there's a significant difference, choose one model, but report the prediction results of the other regression as a sensitivity analysis.</t>
@@ -349,15 +343,9 @@
     <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
   </si>
   <si>
-    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG3:AH9 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH4 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
-  </si>
-  <si>
     <t>Optional – faster charts on a fixed-size dataset:</t>
   </si>
   <si>
-    <t>The seven diagnostic charts read each series from a worksheet-scoped named range (the RegChart* names) built with OFFSET and sized to the live observation count at $Y$8. OFFSET is volatile, so those ranges re-evaluate on every recalculation pass. If your dataset size is stable, you can remove that overhead by pointing each chart series directly at the absolute range the name resolves to — from row 3 (one below the column header) down to row 2+N, where N is the count shown at $Y$8 (for 200 observations, for example ='Regression'!$AM$3:$AM$202). Select the chart, click a series, and replace the ='Regression'!RegChart... reference in the formula bar with the absolute range. The trade-off is that the chart no longer resizes if you add or drop rows — you must re-point it when the row count changes. The named ranges can stay defined; there is no need to delete them.</t>
-  </si>
-  <si>
     <t>Open the Name Manager (Formulas → Name Manager) and update Source_Table (the "Refers To" field) to your table, including its header row — for example =MyTable[#All]. Everything else derives from this one name: the header row, the data body, and the variable list in the MODEL SPECIFICATION block all update automatically. Source_Table points at LifeExpectancyData by default (a curated four-driver Life Expectancy model — Adult Mortality, Alcohol, percentage expenditure, and Status); a second sample table, MileageData (on the Mileage Data sheet), ships with the workbook for a multi-level categorical-encoding demo (MPG ~ Horsepower + Weight + C(Model Year) + C(Origin) — reach it with --regression-dataset auto_mpg). Practice the retarget on either before pointing at your own data.</t>
   </si>
   <si>
@@ -380,6 +368,18 @@
   </si>
   <si>
     <t>Col AX, Residual Output</t>
+  </si>
+  <si>
+    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG4:AH10 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH5 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
+  </si>
+  <si>
+    <t>The seven diagnostic charts read each series from a worksheet-scoped named range (the RegChart* names) built with OFFSET and sized to the live observation count at $AB$9. OFFSET is volatile, so those ranges re-evaluate on every recalculation pass. If your dataset size is stable, you can remove that overhead by pointing each chart series directly at the absolute range the name resolves to — from row 4 (one below the column header) down to row 3+N, where N is the count shown at $AB$9 (for 200 observations, for example ='Regression'!$AP$4:$AP$203). Select the chart, click a series, and replace the ='Regression'!RegChart... reference in the formula bar with the absolute range. The trade-off is that the chart no longer resizes if you add or drop rows — you must re-point it when the row count changes. The named ranges can stay defined; there is no need to delete them.</t>
+  </si>
+  <si>
+    <t>Spikes above F.INV(0.5, p, n-p) — the median of the reference F distribution, so the bar to beat scales with the model's own size — mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a different population, or disproportionately distorts the analysis. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
+  </si>
+  <si>
+    <t>Cook's D &gt; F.INV(0.5, p, n-p) or |PRESS| &gt; 2 × SE for one or more rows.</t>
   </si>
 </sst>
 </file>
@@ -806,17 +806,17 @@
     </row>
     <row r="6" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="90" x14ac:dyDescent="0.25">
@@ -826,7 +826,7 @@
     </row>
     <row r="11" spans="1:1" ht="360" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -856,17 +856,17 @@
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -997,7 +997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -1008,40 +1008,40 @@
         <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1049,128 +1049,128 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1178,13 +1178,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1192,100 +1192,100 @@
         <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="240" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows_code\Statistical_Analysis_Lambda_Catalog\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LocalPython\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33FE3A67-F0AF-4703-B8DD-ACF62AC8A03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55765C50-A18D-4923-97D9-1C1542949950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression Instructions" sheetId="2" r:id="rId1"/>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LocalPython\Statistical_Analysis_Lambda_Catalog\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows_code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55765C50-A18D-4923-97D9-1C1542949950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56BB81F4-176B-4944-B5A9-5455F91C379C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression Instructions" sheetId="2" r:id="rId1"/>
     <sheet name="Diagnostic Guide" sheetId="3" r:id="rId2"/>
+    <sheet name="Modeling Concepts" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
   <si>
     <t>How to use the Regression sheet for Multilinear Regression (MLR)</t>
   </si>
@@ -380,6 +381,115 @@
   </si>
   <si>
     <t>Cook's D &gt; F.INV(0.5, p, n-p) or |PRESS| &gt; 2 × SE for one or more rows.</t>
+  </si>
+  <si>
+    <t>MODELING CONCEPTS — THE WHY BEHIND EACH FEATURE</t>
+  </si>
+  <si>
+    <t>Each feature on the Regression sheet exists to make a specific statistical method available without formulas or add-ins. This table explains that link: the point of the feature, the method it enables, and a concrete situation for using it. For the mechanics of setting a feature up, see the Regression Instructions sheet; for how to read the fitted model's residual plots, see the Diagnostic Guide.</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>The Point</t>
+  </si>
+  <si>
+    <t>Statistical Method</t>
+  </si>
+  <si>
+    <t>Use Case</t>
+  </si>
+  <si>
+    <t>Fixed Effects
+(Role = Fixed Effects)</t>
+  </si>
+  <si>
+    <t>Groups differ in ways you never measured — plant conditions, firm culture, country policy — and those stable differences can drive both the response and the predictors, biasing coefficients. Fixed Effects absorbs a separate intercept for each group so the group differences stop competing with the predictors you actually care about.</t>
+  </si>
+  <si>
+    <t>One-way within transformation: every variable is restated as a deviation from its group's mean, which removes the group intercepts from the fit entirely. Algebraically equal to LSDV (a dummy column per group) without the columns, and the absorbed group degrees of freedom are credited back into inference.</t>
+  </si>
+  <si>
+    <t>Modelling salaries across 12 plants: plant-level pay practices drive both salary and who works where. Set Plant to Role = Fixed Effects and the coefficients answer the within-plant question — holding the plant fixed, what does this predictor change? — with no plant dummy columns cluttering the coefficient table.</t>
+  </si>
+  <si>
+    <t>Reference Levels
+(Categorical predictors)</t>
+  </si>
+  <si>
+    <t>A categorical column cannot enter a regression as text — it has to become numbers. But one 0/1 column per level PLUS an intercept is redundant (perfect multicollinearity), so one level must step aside as the baseline everything else is measured against.</t>
+  </si>
+  <si>
+    <t>Treatment (dummy) coding: a 0/1 column per retained level, with the reference level dropped. Each categorical coefficient reads as a contrast against the reference; the intercept absorbs the reference level's baseline. The default reference is the first-in-sort-order level; type another in column E to override. A typed level not present in the sample is flagged red, never silently fitted.</t>
+  </si>
+  <si>
+    <t>Origin (US / Europe / Japan) predicting MPG: with US as the reference, the Europe coefficient is the Europe-vs-US difference in MPG. Pick the level that makes the contrasts meaningful — an experiment's control group, or the market standard your question is 'compared to what?'</t>
+  </si>
+  <si>
+    <t>Sequence Effects
+(Sequence flag, column H)</t>
+  </si>
+  <si>
+    <t>Panel and repeated-measures data violate the independence assumption — rows within one unit follow each other in time. Lags, differences, and serial-correlation diagnostics all need to know which variable defines that ordering, which is what the Sequence flag declares.</t>
+  </si>
+  <si>
+    <t>Within-group exact-time matching: Lag_By and Difference_By find each group's prior period by matching its time value, never by row position, so a gap in the panel yields #N/A instead of a silently wrong neighbor. The Base Period Δ (your typed override, or the computed candidate — the most common within-group spacing) sets the period step, and the BFN Panel Durbin-Watson tests for serial correlation within groups.</t>
+  </si>
+  <si>
+    <t>Yearly observations per country: set Year to Sequence = TRUE and a year-over-year difference column gives each country's change between its own consecutive years. The Sequence Spacing verdict above the spec tells you whether the panel is regular enough for those features to mean what you think they mean.</t>
+  </si>
+  <si>
+    <t>Log Transforms
+(Transform = Log / Log (drop ≤ 0))</t>
+  </si>
+  <si>
+    <t>Many relationships are multiplicative, not additive — effects are percentages, not absolute amounts. Fitting in log space makes percentages linear, tames skewed data, and turns elasticity models into simple slopes.</t>
+  </si>
+  <si>
+    <t>The fit runs on Ln(y) and/or Ln(x): every statistic (coefficients, R², residuals, prediction intervals) is in log space. The Unit-Space Fit block back-transforms predictions and fit statistics to the original units with Duan smearing — a retransformation correction for the bias of exp(Ln ỹ) under non-constant variance — next to the naive exp() form so the two can be compared. Zeros and negatives have no logarithm: plain Log keeps them in the sample and the fit fails loudly (#N/A, cell turns red); Log (drop ≤ 0) excludes them and reports how many.</t>
+  </si>
+  <si>
+    <t>Price vs. size: a Log response with Log predictors gives an elasticity — each coefficient is the % change in price for a 1% change in its predictor. For a skewed response like income, Log(y) makes the residuals symmetric and the Q-Q plot behave.</t>
+  </si>
+  <si>
+    <t>Interactions
+(Interaction Term / Operation, M/N)</t>
+  </si>
+  <si>
+    <t>One predictor's effect can depend on another's value — a discount that lands differently by market, a drug that scales with dosage. A purely additive model cannot express that dependency; an interaction column can.</t>
+  </si>
+  <si>
+    <t>Pairwise constructed columns in three operations: Product (symmetric), Difference (antisymmetric), Ratio (asymmetric). Width follows the operands: Continuous × Continuous adds 1 column, Continuous × Categorical adds L−1, Categorical × Categorical adds (L₁−1)(L₂−1) — all counted in the Design Columns audit. Interacting a variable with itself under Product is the documented quadratic. An interaction whose main effect is switched off is flagged amber (marginality); declaring both A×B and B×A under Product or Difference is flagged red (duplicate column, singular matrix).</t>
+  </si>
+  <si>
+    <t>Does advertising work equally in every region? Interact Ad Spend (Continuous) with Region (Categorical): the design gains one ad-sensitivity slope per region vs. the reference, and each coefficient answers for its own region. For diminishing returns, interact x with itself under Product to add x².</t>
+  </si>
+  <si>
+    <t>Sample Filtering &amp; Completeness
+(Role = Filter)</t>
+  </si>
+  <si>
+    <t>The fit should answer a question about a specific population, and rows with missing values cannot be part of it. The workbook derives the analysis sample from the spec, so a change of population is a specification change — not hand-deleting rows on the data sheet.</t>
+  </si>
+  <si>
+    <t>A per-row mask ANDed together: every Filter column must be TRUE, the Response must be numeric, and every included Continuous predictor must be numeric (listwise deletion). Categorical predictors impose no completeness condition — a blank category is just not a level. Log (drop ≤ 0) adds its own exclusion layer, and the excluded-row counts surface in the status cells above the spec (B2 / G2) rather than staying silent.</t>
+  </si>
+  <si>
+    <t>Restrict a nationwide demand model to one market segment: add a derived column that is TRUE only for that segment, set its Role to Filter, and every statistic is refit to that population. Retarget the filter later and the sample follows — the data sheet is never touched.</t>
+  </si>
+  <si>
+    <t>Intercept Control
+(C2 toggle)</t>
+  </si>
+  <si>
+    <t>The intercept is the model's baseline — the expected response at zero on every predictor. Usually that baseline is meaningful and should stay; occasionally theory says the response must be zero when the predictors are.</t>
+  </si>
+  <si>
+    <t>A model-level on/off toggle (cell C2). With reference-coded categoricals in the model, turning it OFF is flagged red: each dummy coefficient redefines from a contrast against the reference to an absolute level mean, which is usually not the question being asked. Under Fixed Effects it is flagged because the within transformation demeans the data, and the intercept of demeaned data is an uninterpretable artifact.</t>
+  </si>
+  <si>
+    <t>Theory says cost is zero at zero production, or the instrument reads zero with no input? Turn the intercept off for a regression-through-origin fit. Otherwise leave it on and let it absorb the reference levels' baseline.</t>
   </si>
 </sst>
 </file>
@@ -1291,4 +1401,145 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1D5C19-8245-4AA6-BFBC-8BFCB51F135C}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" customWidth="1"/>
+    <col min="4" max="4" width="46.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" ht="255" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="225" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="255" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows_code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56BB81F4-176B-4944-B5A9-5455F91C379C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F75D6CB4-1E3F-49A4-A5E9-7CB62C5722A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="153">
   <si>
     <t>How to use the Regression sheet for Multilinear Regression (MLR)</t>
   </si>
@@ -341,9 +341,6 @@
     <t>Define your model in the MODEL SPECIFICATION block (columns A–O):</t>
   </si>
   <si>
-    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
-  </si>
-  <si>
     <t>Optional – faster charts on a fixed-size dataset:</t>
   </si>
   <si>
@@ -369,9 +366,6 @@
   </si>
   <si>
     <t>Col AX, Residual Output</t>
-  </si>
-  <si>
-    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG4:AH10 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH5 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
   </si>
   <si>
     <t>The seven diagnostic charts read each series from a worksheet-scoped named range (the RegChart* names) built with OFFSET and sized to the live observation count at $AB$9. OFFSET is volatile, so those ranges re-evaluate on every recalculation pass. If your dataset size is stable, you can remove that overhead by pointing each chart series directly at the absolute range the name resolves to — from row 4 (one below the column header) down to row 3+N, where N is the count shown at $AB$9 (for 200 observations, for example ='Regression'!$AP$4:$AP$203). Select the chart, click a series, and replace the ='Regression'!RegChart... reference in the formula bar with the absolute range. The trade-off is that the chart no longer resizes if you add or drop rows — you must re-point it when the row count changes. The named ranges can stay defined; there is no need to delete them.</t>
@@ -490,6 +484,42 @@
   </si>
   <si>
     <t>Theory says cost is zero at zero production, or the instrument reads zero with no input? Turn the intercept off for a regression-through-origin fit. Otherwise leave it on and let it absorb the reference levels' baseline.</t>
+  </si>
+  <si>
+    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG4:AH10 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH5 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. The constructor builds the interaction columns immediately after the declaring row's own block, so the design matrix stays in specification order: one column for Continuous × Continuous, one per non-reference level for Continuous × Categorical, and one per level pair for Categorical × Categorical. Headers join the two operands' names with the operation's own symbol (e.g. "Weight × Origin: US", "Weight ÷ Displacement"), so a header says what was done as well as what it was done to. An operand that is an excluded Predictor still builds — flagged amber, because an interaction without its main effect is a marginality violation that is usually a mistake but occasionally deliberate. An operand that is not a Predictor or matches no column contributes nothing and stays flagged red — the constructor degrades to the main effect rather than taking the sheet down for one mistyped cell, the same way an invalid Reference Level does. A reciprocal declaration (this row names the other, the other names this one back, both under Product or Difference) is flagged red — a duplicate column would make the Gram matrix singular. Ratio is exempt (B/A is a different column from A/B), and a row naming ITSELF is exempt: self × self under Product is the documented quadratic term. Ratio returns #N/A where the denominator is zero, rather than a #DIV/0! error. Two-way interactions only. One thing is deliberately not automatic: an interaction row in the Prediction Inputs band is an independent input, not recomputed from its operand rows — the band's header note says so rather than silently rewriting one user input because another changed. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
+  </si>
+  <si>
+    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB13) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
+  </si>
+  <si>
+    <t>RESIDUALS UNDER FIXED EFFECTS</t>
+  </si>
+  <si>
+    <t>What you'll see</t>
+  </si>
+  <si>
+    <t>What it means</t>
+  </si>
+  <si>
+    <t>How to read it</t>
+  </si>
+  <si>
+    <t>The response-scale Residual Output headers relabel: Predicted Y, Residuals, and PRESS Residual gain "(Within &lt;FE variable&gt;)" and Y becomes "Deviation from &lt;FE variable&gt; Avg."</t>
+  </si>
+  <si>
+    <t>Once a Fixed Effects row is declared, every diagnostic column is computed from the within (group-demeaned) fit. The model absorbs a separate intercept per group, so each column holds deviations from the group's own average, not from the pooled response. The dimensionless columns (Hat Diagonal, Studentized Residuals, Cook's Distance, Scale-Location, …) keep their names — they were never in response units.</t>
+  </si>
+  <si>
+    <t>The Tier 1 and Tier 2 plots read these same within-group values: a funnel means non-constant variance within groups, a curve means the within-group relationship is misspecified. Between-group differences no longer appear in the residuals at all — absorbing them is the point of Fixed Effects.</t>
+  </si>
+  <si>
+    <t>Each group's Deviation values average zero by construction; Durbin-Watson reads "n/a — FE active" and the BFN Panel Durbin-Watson row below it takes over.</t>
+  </si>
+  <si>
+    <t>The demeaning centers every group on zero, so a large Deviation is a row far from its own group's average — the quantity the model actually fits. Classical Durbin-Watson assumes one ordered series; with a Sequence axis and Fixed Effects the residuals form panels, so serial correlation is read with the Bhargava–Franzini–Narendranathan (1982) panel statistic instead.</t>
+  </si>
+  <si>
+    <t>Treat the BFN cell as the DW cell's replacement while Fixed Effects is active — the classical DW bounds do not apply to panel residuals. The influence flags (Cook's Distance, PRESS) apply unchanged, now measuring influence on the within-group fit.</t>
   </si>
 </sst>
 </file>
@@ -916,7 +946,7 @@
     </row>
     <row r="6" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -934,9 +964,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="360" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -966,17 +996,17 @@
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -986,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1687EF57-B6EB-444E-A46B-98E7D5CA1EC6}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -1118,7 +1148,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -1246,7 +1276,7 @@
         <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>56</v>
@@ -1260,7 +1290,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>56</v>
@@ -1274,7 +1304,7 @@
         <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>68</v>
@@ -1288,13 +1318,13 @@
         <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1302,7 +1332,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>70</v>
@@ -1316,7 +1346,7 @@
         <v>72</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>73</v>
@@ -1381,7 +1411,7 @@
         <v>88</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>89</v>
@@ -1396,6 +1426,46 @@
       </c>
       <c r="C37" s="2" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="270" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1416,7 +1486,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1424,119 +1494,119 @@
     </row>
     <row r="2" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows_code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56BB81F4-176B-4944-B5A9-5455F91C379C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2497202-977F-46D5-92AA-70C3C8E3310D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="166">
   <si>
     <t>How to use the Regression sheet for Multilinear Regression (MLR)</t>
   </si>
@@ -76,9 +76,6 @@
     <t>REGRESSION DIAGNOSTIC GUIDE</t>
   </si>
   <si>
-    <t>Use the charts and flagged cells on the Regression sheet to assess model assumptions. Work through Tier 1 first; investigate Tier 2 only when a Tier 1 plot raises a concern.</t>
-  </si>
-  <si>
     <t>TIER 1 — Review for every model</t>
   </si>
   <si>
@@ -115,16 +112,10 @@
     <t>Studentized Residuals Ranked</t>
   </si>
   <si>
-    <t>Points close to a straight diagonal line. Heavy tails or an S-curve indicate non-normal errors. Check QQ Correlation (Cell P10): below 0.98 = mild concern, below 0.95 = stronger concern.</t>
-  </si>
-  <si>
     <t>Actual vs. Predicted</t>
   </si>
   <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>Points close to a 45° line. A bow or fan shape confirms the same problems seen in Residuals vs. Fitted but from a different angle.</t>
   </si>
   <si>
     <t>TIER 2 — Investigate when Tier 1 raises a concern</t>
@@ -155,17 +146,11 @@
     <t>Studentized Residuals</t>
   </si>
   <si>
-    <t>High leverage alone is not a problem. Combined high leverage and large residual (top-right or bottom-right of the plot) = influential outlier. Hat &gt; 2p/n is flagged red; Hat &gt; 3p/n is additionally bold.</t>
-  </si>
-  <si>
     <t>PRESS Residuals</t>
   </si>
   <si>
     <t>PRESS Residual
 (e / (1 − h))</t>
-  </si>
-  <si>
-    <t>PRESS residuals inflate the ordinary residual by leverage. Bars are ordered by observation number. Large values (|PRESS| &gt; 2 × SE yellow, &gt; 3 × SE red) flag observations whose removal would substantially shift the fitted model.</t>
   </si>
   <si>
     <t>DIAGNOSTIC THRESHOLD REFERENCE</t>
@@ -341,9 +326,6 @@
     <t>Define your model in the MODEL SPECIFICATION block (columns A–O):</t>
   </si>
   <si>
-    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB12) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
-  </si>
-  <si>
     <t>Optional – faster charts on a fixed-size dataset:</t>
   </si>
   <si>
@@ -371,28 +353,16 @@
     <t>Col AX, Residual Output</t>
   </si>
   <si>
-    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG4:AH10 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH5 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. They are placeholders in this release: the dropdowns, the marginality warning (amber when the named Predictor is excluded), and the duplicate-column error (red when two rows declare the same symmetric interaction of each other) are all live, but no constructor builds the columns yet. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
-  </si>
-  <si>
     <t>The seven diagnostic charts read each series from a worksheet-scoped named range (the RegChart* names) built with OFFSET and sized to the live observation count at $AB$9. OFFSET is volatile, so those ranges re-evaluate on every recalculation pass. If your dataset size is stable, you can remove that overhead by pointing each chart series directly at the absolute range the name resolves to — from row 4 (one below the column header) down to row 3+N, where N is the count shown at $AB$9 (for 200 observations, for example ='Regression'!$AP$4:$AP$203). Select the chart, click a series, and replace the ='Regression'!RegChart... reference in the formula bar with the absolute range. The trade-off is that the chart no longer resizes if you add or drop rows — you must re-point it when the row count changes. The named ranges can stay defined; there is no need to delete them.</t>
   </si>
   <si>
-    <t>Spikes above F.INV(0.5, p, n-p) — the median of the reference F distribution, so the bar to beat scales with the model's own size — mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a different population, or disproportionately distorts the analysis. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
-  </si>
-  <si>
     <t>Cook's D &gt; F.INV(0.5, p, n-p) or |PRESS| &gt; 2 × SE for one or more rows.</t>
   </si>
   <si>
     <t>MODELING CONCEPTS — THE WHY BEHIND EACH FEATURE</t>
   </si>
   <si>
-    <t>Each feature on the Regression sheet exists to make a specific statistical method available without formulas or add-ins. This table explains that link: the point of the feature, the method it enables, and a concrete situation for using it. For the mechanics of setting a feature up, see the Regression Instructions sheet; for how to read the fitted model's residual plots, see the Diagnostic Guide.</t>
-  </si>
-  <si>
     <t>Feature</t>
-  </si>
-  <si>
-    <t>The Point</t>
   </si>
   <si>
     <t>Statistical Method</t>
@@ -490,6 +460,115 @@
   </si>
   <si>
     <t>Theory says cost is zero at zero production, or the instrument reads zero with no input? Turn the intercept off for a regression-through-origin fit. Otherwise leave it on and let it absorb the reference levels' baseline.</t>
+  </si>
+  <si>
+    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG4:AH10 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH5 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. The interaction column is built into the design matrix automatically: Continuous × Continuous adds 1 column, Continuous × Categorical adds one per retained level, and Categorical × Categorical adds the full product of the two. Naming this row's own variable with Operation = Product is the documented way to declare a quadratic (x²) term. An interaction whose mate is switched off (Include = FALSE) still builds and is flagged amber as a marginality warning; a reciprocal declaration — two rows naming each other under Product or Difference — is flagged red, because it would duplicate or negate a column and make the matrix singular. Interaction rows also appear in PREDICTION INPUTS; leave them at the Training Mean defaults or type scenario values. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
+  </si>
+  <si>
+    <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB13) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
+  </si>
+  <si>
+    <t>Each feature on the Regression sheet exists to make a specific statistical method available without formulas or add-ins. This table explains that link: what problem the feature solves, the method it enables, and a concrete situation for using it. For the mechanics of setting a feature up, see the Regression Instructions sheet; for how to read the fitted model's residual plots, see the Diagnostic Guide.</t>
+  </si>
+  <si>
+    <t>What Problem It Solves</t>
+  </si>
+  <si>
+    <t>PLANNED FEATURES — DECLARED IN THE SHEET, NOT YET BUILT</t>
+  </si>
+  <si>
+    <t>The features below are declared in the sheet's structure — a Role value in the dropdown, a reserved column — but no formula builds them in this release. Each row states what problem the feature will solve when it ships, and what to use in the meantime.</t>
+  </si>
+  <si>
+    <t>Weight — WLS
+(Role = Weight, v3.7)
+PLANNED, future release</t>
+  </si>
+  <si>
+    <t>Some observations are known to be noisier than others — each row averages a different number of underlying readings, or a variance you can quantify at row level. OLS gives the noisy rows the same vote as the precise ones.</t>
+  </si>
+  <si>
+    <t>Weighted Least Squares: each row enters the fit scaled by its known variance, so precise observations dominate. The Weight Role will name the column carrying that variance.</t>
+  </si>
+  <si>
+    <t>Today's workaround is the Diagnostic Guide's heteroscedasticity guidance: a Log transform on the response, or an interaction / quadratic term when the variance tracks a predictor's mean.</t>
+  </si>
+  <si>
+    <t>Cluster
+(Role = Cluster, v3.5)
+PLANNED, future release</t>
+  </si>
+  <si>
+    <t>Rows collected in groups — plants, firms, countries — share unmodeled shocks, so nominally-independent standard errors are too optimistic (they overstate significance).</t>
+  </si>
+  <si>
+    <t>Clustered-robust variance estimator: the same coefficients, with standard errors that allow arbitrary correlation within a group. Partially forward-wired — the Role slot and a dormant branch in Serial_Correlation_Group() await the estimator.</t>
+  </si>
+  <si>
+    <t>Survey or panel data where rows within one cluster move together: name the cluster column and the P-values and confidence intervals stop assuming every row is independent.</t>
+  </si>
+  <si>
+    <t>Time
+(Role = Time, v3.6)
+PLANNED, future release</t>
+  </si>
+  <si>
+    <t>A panel needs an explicit time index distinct from 'which group a row belongs to' — lag and difference features must follow time within a unit, not sheet order.</t>
+  </si>
+  <si>
+    <t>Time-index designation: the Role names the column holding each row's time value; Lag_By / Difference_By and the future Time Series sheet are its consumers. The Role ships first, the sheet last.</t>
+  </si>
+  <si>
+    <t>Until then, the Sequence flag (column H) plus its Sequence Period override already carries the ordering axis for the shipped lag/difference features.</t>
+  </si>
+  <si>
+    <t>Two-way Fixed Effects
+(v3.8)
+PLANNED, future release</t>
+  </si>
+  <si>
+    <t>Sometimes the stable nuisance is two-dimensional — both the plant AND the year leave a fixed mark on every observation, and absorbing only one of them leaves the other confounding the coefficients.</t>
+  </si>
+  <si>
+    <t>Absorb_Two_Way_Fixed_Effects: the within transformation applied along two group axes at once. Today at most ONE Fixed Effects row is legal — two or more is a red spec error, by design, until this lands.</t>
+  </si>
+  <si>
+    <t>Plant-and-year panels: for now, keep one Fixed Effects row and use a Filter to narrow the sample, or dummy-code the second axis as a Categorical predictor.</t>
+  </si>
+  <si>
+    <t>Order
+(column F)
+PLANNED, future release</t>
+  </si>
+  <si>
+    <t>Term order in the coefficient table currently follows the source table's column order — fine for every model so far, but a hand-authored spec may want terms presented in a chosen sequence.</t>
+  </si>
+  <si>
+    <t>A reserved, hidden column (width 0): it will control each spec row's position in the constructed design matrix and the coefficient table. No formula reads it in this release.</t>
+  </si>
+  <si>
+    <t>Nothing to do today — the column is hidden and ignored; leave it blank if you reveal it.</t>
+  </si>
+  <si>
+    <t>Use the charts and flagged cells on the Regression sheet to assess model assumptions. Work through Tier 1 first; investigate Tier 2 only when a Tier 1 plot raises a concern. Each chart's title carries the live statistics it judges against — the Q-Q correlation, the Adjusted R², the mean leverage, the Cook's Distance cutoff and the PRESS total — so a chart can be read without scrolling back to its source cell.</t>
+  </si>
+  <si>
+    <t>Points close to a straight diagonal line. Heavy tails or an S-curve indicate non-normal errors. Check QQ Correlation (Cell P10): below 0.98 = mild concern, below 0.95 = stronger concern. The chart title itself shows the live r and appends a '— check normality' warning when it falls below 0.95, matching the table's red threshold.</t>
+  </si>
+  <si>
+    <t>Points close to a 45° line. A bow or fan shape confirms the same problems seen in Residuals vs. Fitted but from a different angle. The chart title shows the response name and the live Adjusted R², so the fit's headline quality is on the plot itself.</t>
+  </si>
+  <si>
+    <t>Spikes above F.INV(0.5, p, n-p) — the median of the reference F distribution, so the bar to beat scales with the model's own size — mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. The title prints the live cutoff, so the bar to beat is visible on the plot itself, and bars above it carry data labels naming the row. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a different population, or disproportionately distorts the analysis. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
+  </si>
+  <si>
+    <t>High leverage alone is not a problem. Combined high leverage and large residual (top-right or bottom-right of the plot) = influential outlier. Hat &gt; 2p/n is flagged red; Hat &gt; 3p/n is additionally bold. The title prints the live mean leverage (p/n), so 'Hat &gt; 2p/n' reads directly as 'more than twice the printed mean.'</t>
+  </si>
+  <si>
+    <t>PRESS residuals inflate the ordinary residual by leverage. Bars are ordered by observation number. Large values (|PRESS| &gt; 2 × SE yellow, &gt; 3 × SE red) flag observations whose removal would substantially shift the fitted model. The chart title carries the live PRESS total.</t>
+  </si>
+  <si>
+    <t>These thresholds surface in three places: the flagged cells named above, the diagnostic and audit cells the table cites, and the chart titles and data labels on the Regression sheet — a chart can be judged against its own printed cutoff without scrolling back to its source cell.</t>
   </si>
 </sst>
 </file>
@@ -916,17 +995,17 @@
     </row>
     <row r="6" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="90" x14ac:dyDescent="0.25">
@@ -934,9 +1013,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="360" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -966,17 +1045,17 @@
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -986,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1687EF57-B6EB-444E-A46B-98E7D5CA1EC6}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -1002,14 +1081,14 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1017,63 +1096,63 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1081,77 +1160,77 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="240" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="195" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1159,243 +1238,248 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="4" t="s">
+    </row>
+    <row r="35" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="120" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="2" t="s">
+    </row>
+    <row r="36" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="105" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="2" t="s">
+    </row>
+    <row r="37" spans="1:3" ht="240" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="120" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="38" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="240" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="150" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1405,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1D5C19-8245-4AA6-BFBC-8BFCB51F135C}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -1416,7 +1500,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1424,119 +1508,216 @@
     </row>
     <row r="2" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="225" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="180" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="225" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="C16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/templates/static_sheets.xlsx
+++ b/templates/static_sheets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen_Colodner\windows_code\Statistical_Analysis_Lambda_Catalog\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2497202-977F-46D5-92AA-70C3C8E3310D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D477202-9FFB-4C3D-B175-167A56CC28CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{1411C739-6A2D-448E-B19F-D2DD9A0E5CC5}"/>
   </bookViews>
@@ -43,18 +43,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="166">
   <si>
-    <t>How to use the Regression sheet for Multilinear Regression (MLR)</t>
-  </si>
-  <si>
     <t>To analyze your own dataset, copy the Regression sheet into your workbook (right-click the tab → Move or Copy). This carries over all workbook-scoped LAMBDA functions as well as the sheet-scoped names the Regression sheet uses.</t>
   </si>
   <si>
     <t>Ensure your data is organized as a structured Excel table. Select the range including column headers and press Ctrl+T, or go to Home → Format as Table.</t>
   </si>
   <si>
-    <t>Point the sheet at your data (one edit):</t>
-  </si>
-  <si>
     <t>For each included Predictor, set its Type. Continuous predictors enter the design matrix as-is. Categorical predictors are dummy-coded automatically: each level except the reference level becomes a 0/1 column with a level-qualified name (e.g. "Status: Developing"). The reference level defaults to the first level in sort order; type a level into Reference Level to override it (the cell turns red if that level does not exist in the analysis sample). The Levels and Reference In Use columns display what the model will do: the distinct level count in the analysis sample, and the reference actually in effect. A categorical with one level (or an invalid reference) is flagged red and contributes no columns — the rest of the model still computes.</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>Which rows are used:</t>
   </si>
   <si>
-    <t>The analysis sample is derived automatically — a row is included when the Response is numeric, every included Continuous predictor is numeric, and every Filter column is truthy. There is nothing to configure beyond the Roles. Note that Categorical predictors impose no completeness requirement: rows with a blank category still enter the sample (all of that variable's dummies are blank there) unless a Filter excludes them.</t>
-  </si>
-  <si>
     <t>Optional — point prediction:</t>
   </si>
   <si>
@@ -116,9 +107,6 @@
   </si>
   <si>
     <t>Y</t>
-  </si>
-  <si>
-    <t>TIER 2 — Investigate when Tier 1 raises a concern</t>
   </si>
   <si>
     <t>Scale-Location</t>
@@ -128,9 +116,6 @@
 (√|Studentized Residuals|)</t>
   </si>
   <si>
-    <t>Flat horizontal spread of points = homoscedasticity. An upward trend confirms heteroscedasticity flagged in Tier 1. Yellow cells: value &gt; √2 ≈ 1.41; red cells: value &gt; √3 ≈ 1.73.</t>
-  </si>
-  <si>
     <t>Cook's Distance</t>
   </si>
   <si>
@@ -195,9 +180,6 @@
     <t>PRESS R²</t>
   </si>
   <si>
-    <t>Cell P5, Diagnostics</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
@@ -207,9 +189,6 @@
     <t>QQ Correlation</t>
   </si>
   <si>
-    <t>Cell P10, Diagnostics</t>
-  </si>
-  <si>
     <t>&lt; 0.98  (mild non-normality)</t>
   </si>
   <si>
@@ -217,9 +196,6 @@
   </si>
   <si>
     <t>Significance F</t>
-  </si>
-  <si>
-    <t>Cell Q15, ANOVA Table</t>
   </si>
   <si>
     <t>P-value &gt; alpha  (model not significant)</t>
@@ -292,9 +268,6 @@
   </si>
   <si>
     <t>Q-Q plot shows heavy tails or S-curve; QQ Correlation &lt; 0.98.</t>
-  </si>
-  <si>
-    <t>With n &gt; 100 moderate departures rarely invalidate inference. For small n, consider robust standard errors or a bootstrap Confidence Interval approach.</t>
   </si>
   <si>
     <t>Influential observations
@@ -329,9 +302,6 @@
     <t>Optional – faster charts on a fixed-size dataset:</t>
   </si>
   <si>
-    <t>Open the Name Manager (Formulas → Name Manager) and update Source_Table (the "Refers To" field) to your table, including its header row — for example =MyTable[#All]. Everything else derives from this one name: the header row, the data body, and the variable list in the MODEL SPECIFICATION block all update automatically. Source_Table points at LifeExpectancyData by default (a curated four-driver Life Expectancy model — Adult Mortality, Alcohol, percentage expenditure, and Status); a second sample table, MileageData (on the Mileage Data sheet), ships with the workbook for a multi-level categorical-encoding demo (MPG ~ Horsepower + Weight + C(Model Year) + C(Origin) — reach it with --regression-dataset auto_mpg). Practice the retarget on either before pointing at your own data.</t>
-  </si>
-  <si>
     <t>Col AE, Coefficients</t>
   </si>
   <si>
@@ -401,9 +371,6 @@
 (Sequence flag, column H)</t>
   </si>
   <si>
-    <t>Panel and repeated-measures data violate the independence assumption — rows within one unit follow each other in time. Lags, differences, and serial-correlation diagnostics all need to know which variable defines that ordering, which is what the Sequence flag declares.</t>
-  </si>
-  <si>
     <t>Within-group exact-time matching: Lag_By and Difference_By find each group's prior period by matching its time value, never by row position, so a gap in the panel yields #N/A instead of a silently wrong neighbor. The Base Period Δ (your typed override, or the computed candidate — the most common within-group spacing) sets the period step, and the BFN Panel Durbin-Watson tests for serial correlation within groups.</t>
   </si>
   <si>
@@ -414,15 +381,6 @@
 (Transform = Log / Log (drop ≤ 0))</t>
   </si>
   <si>
-    <t>Many relationships are multiplicative, not additive — effects are percentages, not absolute amounts. Fitting in log space makes percentages linear, tames skewed data, and turns elasticity models into simple slopes.</t>
-  </si>
-  <si>
-    <t>The fit runs on Ln(y) and/or Ln(x): every statistic (coefficients, R², residuals, prediction intervals) is in log space. The Unit-Space Fit block back-transforms predictions and fit statistics to the original units with Duan smearing — a retransformation correction for the bias of exp(Ln ỹ) under non-constant variance — next to the naive exp() form so the two can be compared. Zeros and negatives have no logarithm: plain Log keeps them in the sample and the fit fails loudly (#N/A, cell turns red); Log (drop ≤ 0) excludes them and reports how many.</t>
-  </si>
-  <si>
-    <t>Price vs. size: a Log response with Log predictors gives an elasticity — each coefficient is the % change in price for a 1% change in its predictor. For a skewed response like income, Log(y) makes the residuals symmetric and the Q-Q plot behave.</t>
-  </si>
-  <si>
     <t>Interactions
 (Interaction Term / Operation, M/N)</t>
   </si>
@@ -453,16 +411,7 @@
 (C2 toggle)</t>
   </si>
   <si>
-    <t>The intercept is the model's baseline — the expected response at zero on every predictor. Usually that baseline is meaningful and should stay; occasionally theory says the response must be zero when the predictors are.</t>
-  </si>
-  <si>
-    <t>A model-level on/off toggle (cell C2). With reference-coded categoricals in the model, turning it OFF is flagged red: each dummy coefficient redefines from a contrast against the reference to an absolute level mean, which is usually not the question being asked. Under Fixed Effects it is flagged because the within transformation demeans the data, and the intercept of demeaned data is an uninterpretable artifact.</t>
-  </si>
-  <si>
     <t>Theory says cost is zero at zero production, or the instrument reads zero with no input? Turn the intercept off for a regression-through-origin fit. Otherwise leave it on and let it absorb the reference levels' baseline.</t>
-  </si>
-  <si>
-    <t>If your table has more columns than the shipped dataset, fill in Role, Include, and Type for the extra specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet. The Transform column offers Log on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG4:AH10 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH5 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. Under Log, the Duan point estimate does not sit at the centre of the four Naive CI/PI bounds (the conditional mean is offset from the conditional median). Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). The Sequence column marks at most one variable as the ordering axis for future lag/difference/serial-correlation features — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted — never a silent 1. The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. The interaction column is built into the design matrix automatically: Continuous × Continuous adds 1 column, Continuous × Categorical adds one per retained level, and Categorical × Categorical adds the full product of the two. Naming this row's own variable with Operation = Product is the documented way to declare a quadratic (x²) term. An interaction whose mate is switched off (Include = FALSE) still builds and is flagged amber as a marginality warning; a reciprocal declaration — two rows naming each other under Product or Difference — is flagged red, because it would duplicate or negate a column and make the matrix singular. Interaction rows also appear in PREDICTION INPUTS; leave them at the Training Mean defaults or type scenario values. The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
   </si>
   <si>
     <t>Enter a value for each design-matrix column in the orange cells under PREDICTION INPUTS (column AK) — one row per constructed column, including one per dummy (use 1 for the scenario's level, 0 for its siblings; no Intercept row — the model's own baseline is handled automatically). The Training Mean column beside the inputs shows each column's mean over the analysis sample, which is also the prefilled default — so the untouched prediction is at the data's center. Results appear in the PREDICTION OUTPUTS box above as both a mean-response confidence interval (CI) and a wider new-observation prediction interval (PI); the confidence level is controlled by the Alpha cell (AB13) in REGRESSION OUTPUTS. If a Fixed Effects variable is declared, the FE Group cell above the inputs selects which group's own average the prediction is anchored to.</t>
@@ -550,18 +499,6 @@
     <t>Nothing to do today — the column is hidden and ignored; leave it blank if you reveal it.</t>
   </si>
   <si>
-    <t>Use the charts and flagged cells on the Regression sheet to assess model assumptions. Work through Tier 1 first; investigate Tier 2 only when a Tier 1 plot raises a concern. Each chart's title carries the live statistics it judges against — the Q-Q correlation, the Adjusted R², the mean leverage, the Cook's Distance cutoff and the PRESS total — so a chart can be read without scrolling back to its source cell.</t>
-  </si>
-  <si>
-    <t>Points close to a straight diagonal line. Heavy tails or an S-curve indicate non-normal errors. Check QQ Correlation (Cell P10): below 0.98 = mild concern, below 0.95 = stronger concern. The chart title itself shows the live r and appends a '— check normality' warning when it falls below 0.95, matching the table's red threshold.</t>
-  </si>
-  <si>
-    <t>Points close to a 45° line. A bow or fan shape confirms the same problems seen in Residuals vs. Fitted but from a different angle. The chart title shows the response name and the live Adjusted R², so the fit's headline quality is on the plot itself.</t>
-  </si>
-  <si>
-    <t>Spikes above F.INV(0.5, p, n-p) — the median of the reference F distribution, so the bar to beat scales with the model's own size — mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. The title prints the live cutoff, so the bar to beat is visible on the plot itself, and bars above it carry data labels naming the row. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a different population, or disproportionately distorts the analysis. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
-  </si>
-  <si>
     <t>High leverage alone is not a problem. Combined high leverage and large residual (top-right or bottom-right of the plot) = influential outlier. Hat &gt; 2p/n is flagged red; Hat &gt; 3p/n is additionally bold. The title prints the live mean leverage (p/n), so 'Hat &gt; 2p/n' reads directly as 'more than twice the printed mean.'</t>
   </si>
   <si>
@@ -569,6 +506,73 @@
   </si>
   <si>
     <t>These thresholds surface in three places: the flagged cells named above, the diagnostic and audit cells the table cites, and the chart titles and data labels on the Regression sheet — a chart can be judged against its own printed cutoff without scrolling back to its source cell.</t>
+  </si>
+  <si>
+    <t>How to use the Regression sheet for Multiple Linear Regression (MLR)</t>
+  </si>
+  <si>
+    <t>Connect the sheet to your data:</t>
+  </si>
+  <si>
+    <t>Open the Name Manager (Formulas → Name Manager) and update Source_Table (the "Refers To" field) to your table, including its header row — for example =MyTable[#All]. Everything else derives from this one name: the header row, the data body, and the variable list in the MODEL SPECIFICATION block all update automatically. Source_Table points at LifeExpectancyData by default (a curated four-driver Life Expectancy model — Adult Mortality, Alcohol, percentage expenditure, and Status); a second sample table, MileageData (on the Mileage Data sheet), ships with the workbook for a multi-level categorical-encoding demo (MPG ~ Horsepower + Weight + C(Model Year) + C(Origin)). You can use a supplied table or your own Excel Table. After changing the source, review every Role, Include setting, and Type; existing inputs are not inferred from the new headers.</t>
+  </si>
+  <si>
+    <t>The intercept is the model's baseline — the expected response at zero on every predictor. Keep the intercept unless the model requires a zero response when all predictors are zero; the baseline need not itself be a meaningful observed case.</t>
+  </si>
+  <si>
+    <t>A model-level on/off toggle (cell C2). With reference-coded categoricals in the model, turning it OFF is flagged red: the workbook still drops the reference category, so removing the intercept also constrains the reference baseline to zero. Under Fixed Effects it is flagged because the within transformation demeans the data, and the intercept of demeaned data is an uninterpretable artifact.</t>
+  </si>
+  <si>
+    <t>Log transforms can represent multiplicative relationships. They change the scale on which the model is fitted and its coefficients are interpreted; they do not guarantee an adequate fit or symmetric residuals.</t>
+  </si>
+  <si>
+    <t>Only variables marked Log are transformed. Logging a predictor alone leaves the response and residuals in response units. When the response is logged, Naive exponentiates its fitted log value; Duan also multiplies by the average of exp(residuals). This common smearing factor estimates an original-unit conditional mean only when the error retransformation factor is constant across predictor values. It does not generally correct heteroscedasticity. Naive represents a conditional median when log errors have conditional median zero. Original-unit interval bounds always use Naive; they are not confidence bounds for the Duan-adjusted mean. Zeros and negatives have no logarithm: plain Log keeps them in the sample and the fit returns #N/A and flags the Transform cell red; Log (drop ≤ 0) excludes them and reports how many.</t>
+  </si>
+  <si>
+    <t>In a log-log model without interactions, a coefficient gives the proportional change in the fitted geometric mean of the response for a proportional change in that predictor, holding other predictors fixed. For small changes, a 1% predictor increase corresponds to approximately that coefficient percent change in the fitted response. Inspect residual plots after transformation.</t>
+  </si>
+  <si>
+    <t>Panel and repeated-measures data can violate the independence assumption — rows within one unit follow each other in time. Lags, differences, and serial-correlation diagnostics all need to know which variable defines that ordering, which is what the Sequence flag declares.</t>
+  </si>
+  <si>
+    <t>Use the charts and flagged cells on the Regression sheet to assess model assumptions. Start with Tier 1, then review Tier 2 for spread and influence even if Tier 1 looks clear. Thresholds are screening rules, not universal tests of model validity. Chart titles display statistics — the Q-Q correlation, the Adjusted R², the mean leverage, the Cook's Distance cutoff and the PRESS total — so a chart can be read without scrolling back to its source cell.</t>
+  </si>
+  <si>
+    <t>Points close to a straight diagonal line. Heavy tails or an S-curve indicate non-normal errors. Check QQ Correlation (Cell AE11): below 0.98 = mild concern, below 0.95 = stronger concern. The chart title itself shows the live r and appends a '— check normality' warning when it falls below 0.95, matching the table's red threshold.</t>
+  </si>
+  <si>
+    <t>Points close to a 45° line. A bow or fan shape can suggest the same problems seen in Residuals vs. Fitted but from a different angle. The chart title shows the response name and the live Adjusted R², so the fit's headline quality is on the plot itself.</t>
+  </si>
+  <si>
+    <t>TIER 2 — Review spread and influence</t>
+  </si>
+  <si>
+    <t>A roughly horizontal spread is consistent with constant error variance. A trend suggests changing variance; inspect it alongside Residuals vs. Fitted. Yellow cells: value &gt; √2 ≈ 1.41; red cells: value &gt; √3 ≈ 1.73.</t>
+  </si>
+  <si>
+    <t>Spikes above F.INV(0.5, p, n-p) — the median of the reference F distribution, so the bar to beat scales with the model's own size — mark observations with outsized influence on the fitted coefficients. Bars are ordered by observation number. The title prints the live cutoff, so the bar to beat is visible on the plot itself, and bars above it carry data labels naming the row. Inspect those rows for data entry errors or genuine outliers before removing them. Remove outliers only when you have a definitive, non-statistical reason to believe the data point is invalid, comes from a population excluded by the study definition, or is otherwise outside the prespecified analysis scope. Never filter out data solely because it is an extreme statistical value, as doing so can introduce bias and erase genuine insights.</t>
+  </si>
+  <si>
+    <t>Cell AE6, Diagnostics</t>
+  </si>
+  <si>
+    <t>Cell AE11, Diagnostics</t>
+  </si>
+  <si>
+    <t>Cell AF16, ANOVA Table</t>
+  </si>
+  <si>
+    <t>Assess the severity of the departure and the sampling design; there is no universal sample-size cutoff that makes it harmless. Robust standard errors address variance misspecification, not all non-normality. A bootstrap must respect dependence in the data. These alternatives require tools beyond this template.</t>
+  </si>
+  <si>
+    <t>Review Role for every source column, and Include and Type for each Predictor; fill these in for any additional specification rows — the dropdowns are available all the way down. A row with a blank Role is ignored. The Order column is a placeholder for a future version and is not read by any formula; it is hidden on the sheet.
+The Transform column offers Log and Log (drop ≤ 0) on the Response row and on Continuous Predictor rows: the model fits in natural-log space for that variable, and affected outputs are labeled "(Log)" — but the Unit-Space Fit block at AG4:AH10 reports the back-transformed R² / Adj R² / RMSE in original units (Duan smearing by default, Naive on the AH5 toggle), and the Prediction Outputs block's Original Units column (AL) carries the back-transformed point estimate and the four CI/PI bounds. The two new Residual Output columns (AZ, BA) carry Predicted Y and Residual in original units. With a Log response, interval bounds always use Naive back-transformation, regardless of the toggle. They are not confidence bounds for the Duan-adjusted mean. Log is not valid on a Categorical Predictor; setting it there flags the cell red and the fit still runs with that row's Transform ignored (dummy-coded as usual). Plain Log leaves nonpositive values in the sample and returns #N/A; Log (drop ≤ 0) excludes them and reports the count.
+The Sequence column marks at most one variable as the ordering axis used by lag/difference functions and serial-correlation diagnostics — it is independent of Role and Type (a Predictor can also be the sequence axis). Leave it blank for non-panel data; marking two or more rows shows a red error in the status cell above the column. The Sequence Period column (I) is the typed override input: type a number on the flagged row to declare a Δ that differs from the candidate. The Period In Use column (J) is the live companion — it shows the typed override if column I is non-blank, otherwise the computed candidate (the most common gap between consecutive periods within a group). Lag_By and Difference_By fall back to Base_Period_Delta() when their [delta] argument is omitted.
+The Interaction Term (M) and Interaction Operation (N) columns declare an interaction between this row and another Predictor — pick the other variable and one of Product, Difference, or Ratio. The interaction column is built into the design matrix automatically: Continuous × Continuous adds 1 column, Continuous × Categorical adds one per retained level, and Categorical × Categorical adds the full product of the two. Naming this row's own variable with Operation = Product is the documented way to declare a quadratic (x²) term. An interaction whose mate is switched off (Include = FALSE) still builds and is flagged amber as a marginality warning; a reciprocal declaration — two rows naming each other under Product or Difference — is flagged red, because it would duplicate or negate a column and make the matrix singular. Interaction rows also appear in PREDICTION INPUTS; leave them at the Training Mean defaults or type scenario values.
+The Design Columns column (O) shows how many design-matrix columns each row contributes — 1 for a Continuous predictor, one less than the Levels count for a Categorical one. The total above it, with the intercept added, is the full width of the constructed design matrix; it turns amber on a model wide enough to be slow and red on one too wide for the sheet.</t>
+  </si>
+  <si>
+    <t>The analysis sample is derived automatically — a row is included when the Response is numeric, every included Continuous predictor is numeric, and every Filter column is truthy. Include settings and Log (drop ≤ 0) also affect the sample. Categorical predictors impose no completeness requirement: rows with a blank category still enter the sample (all of that variable's dummies are blank there) unless a Filter excludes them.</t>
   </si>
 </sst>
 </file>
@@ -975,87 +979,87 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>8</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1075,20 +1079,20 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="225" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1096,63 +1100,63 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1160,77 +1164,77 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="240" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1238,248 +1242,248 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="225" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>82</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="240" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1500,7 +1504,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1508,124 +1512,124 @@
     </row>
     <row r="2" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="225" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="345" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1633,91 +1637,91 @@
     </row>
     <row r="14" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
